--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/hoofdfunctie_stedenbouw/hoofdfunctie_stedenbouw.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/hoofdfunctie_stedenbouw/hoofdfunctie_stedenbouw.xlsx
@@ -442,7 +442,7 @@
         <v>Vorm van recreatie die niet langer duurt dan een dag, en waarbij dus geen sprake is van overnachting</v>
       </c>
       <c r="D2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E2" t="str">
         <v>Dagrecreatie, met inbegrip van sport</v>
@@ -454,7 +454,7 @@
         <v>Dagrecreatie, met inbegrip van sport</v>
       </c>
       <c r="H2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I2" t="str">
         <v>null</v>
@@ -474,7 +474,7 @@
         <v>Bedrijfstak die zich bezighoudt met eten, drinken en dansgelegenheden. Horeca, maar dan zonder de logies.</v>
       </c>
       <c r="D3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E3" t="str">
         <v>Dancing, restaurant en café</v>
@@ -486,7 +486,7 @@
         <v>Dancing, restaurant en café</v>
       </c>
       <c r="H3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I3" t="str">
         <v>null</v>
@@ -506,7 +506,7 @@
         <v>Bedrijfstak die zich bezighoudt met de verkoop van fysieke goederen aan consumenten</v>
       </c>
       <c r="D4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E4" t="str">
         <v>Detailhandel</v>
@@ -518,7 +518,7 @@
         <v>Detailhandel</v>
       </c>
       <c r="H4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I4" t="str">
         <v>http://www.eionet.europa.eu/gemet/concept/7193</v>
@@ -538,7 +538,7 @@
         <v>Voorzieningen die gericht zijn op de bevordering van het algemeen belang en die ten dienste van de gemeenschap worden gesteld (Bron: 8 JULI 1997. Omzendbrief betreffende de inrichting en de toepassing van de ontwerp-gewestplannen en gewestplannen, gewijzigd via omzendbrief dd. 25/1/2002 en 25/10/2002)</v>
       </c>
       <c r="D5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E5" t="str">
         <v>Gemeenschapsvoorzieningen en openbare nutsvoorzieningen</v>
@@ -550,7 +550,7 @@
         <v>Gemeenschapsvoorzieningen en openbare nutsvoorzieningen</v>
       </c>
       <c r="H5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I5" t="str">
         <v>null</v>
@@ -570,7 +570,7 @@
         <v>Bedrijfstak die zich bezighoudt met de verwerking van grondstoffen tot (half)producten</v>
       </c>
       <c r="D6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E6" t="str">
         <v>Industrie en bedrijvigheid</v>
@@ -582,7 +582,7 @@
         <v>Industrie en bedrijvigheid</v>
       </c>
       <c r="H6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I6" t="str">
         <v>http://www.eionet.europa.eu/gemet/concept/19</v>
@@ -602,7 +602,7 @@
         <v>Bedrijfstak die zich bezighoudt met het verlenen van diensten, inclusief administratieve werkzaamheden en intellectuele diensten.</v>
       </c>
       <c r="D7" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E7" t="str">
         <v>Kantoorfunctie, dienstverlening en vrije beroepen</v>
@@ -614,7 +614,7 @@
         <v>Kantoorfunctie, dienstverlening en vrije beroepen</v>
       </c>
       <c r="H7" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I7" t="str">
         <v>null</v>
@@ -634,7 +634,7 @@
         <v>Bedrijfstak die zich bezighoudt met de productie van paddestoelen, planten en dieren</v>
       </c>
       <c r="D8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E8" t="str">
         <v>Land- en tuinbouw in de ruime zin</v>
@@ -646,7 +646,7 @@
         <v>Land- en tuinbouw in de ruime zin</v>
       </c>
       <c r="H8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I8" t="str">
         <v>http://www.eionet.europa.eu/gemet/concept/232</v>
@@ -666,7 +666,7 @@
         <v>Werking ten behoeve van de krijgsmacht van de staat</v>
       </c>
       <c r="D9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E9" t="str">
         <v>Militaire functie</v>
@@ -678,7 +678,7 @@
         <v>Militaire functie</v>
       </c>
       <c r="H9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I9" t="str">
         <v>null</v>
@@ -698,7 +698,7 @@
         <v>Vorm van recreatie waarbij de recreant voor een bepaalde tijd, maar ten minste een nacht, in het recreatiegebied of de toeristische plaats verblijft</v>
       </c>
       <c r="D10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E10" t="str">
         <v>Verblijfsrecreatie</v>
@@ -710,7 +710,7 @@
         <v>Verblijfsrecreatie</v>
       </c>
       <c r="H10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I10" t="str">
         <v>null</v>
@@ -730,7 +730,7 @@
         <v>Huisvesting van een gezin of alleenstaande</v>
       </c>
       <c r="D11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E11" t="str">
         <v>Wonen</v>
@@ -742,7 +742,7 @@
         <v>Wonen</v>
       </c>
       <c r="H11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I11" t="str">
         <v>null</v>
@@ -753,7 +753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="B12" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>

--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/hoofdfunctie_stedenbouw/hoofdfunctie_stedenbouw.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/hoofdfunctie_stedenbouw/hoofdfunctie_stedenbouw.xlsx
@@ -442,7 +442,7 @@
         <v>Vorm van recreatie die niet langer duurt dan een dag, en waarbij dus geen sprake is van overnachting</v>
       </c>
       <c r="D2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E2" t="str">
         <v>Dagrecreatie, met inbegrip van sport</v>
@@ -454,7 +454,7 @@
         <v>Dagrecreatie, met inbegrip van sport</v>
       </c>
       <c r="H2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I2" t="str">
         <v>null</v>
@@ -474,7 +474,7 @@
         <v>Bedrijfstak die zich bezighoudt met eten, drinken en dansgelegenheden. Horeca, maar dan zonder de logies.</v>
       </c>
       <c r="D3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E3" t="str">
         <v>Dancing, restaurant en café</v>
@@ -486,7 +486,7 @@
         <v>Dancing, restaurant en café</v>
       </c>
       <c r="H3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I3" t="str">
         <v>null</v>
@@ -506,7 +506,7 @@
         <v>Bedrijfstak die zich bezighoudt met de verkoop van fysieke goederen aan consumenten</v>
       </c>
       <c r="D4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E4" t="str">
         <v>Detailhandel</v>
@@ -518,7 +518,7 @@
         <v>Detailhandel</v>
       </c>
       <c r="H4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I4" t="str">
         <v>http://www.eionet.europa.eu/gemet/concept/7193</v>
@@ -538,7 +538,7 @@
         <v>Voorzieningen die gericht zijn op de bevordering van het algemeen belang en die ten dienste van de gemeenschap worden gesteld (Bron: 8 JULI 1997. Omzendbrief betreffende de inrichting en de toepassing van de ontwerp-gewestplannen en gewestplannen, gewijzigd via omzendbrief dd. 25/1/2002 en 25/10/2002)</v>
       </c>
       <c r="D5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E5" t="str">
         <v>Gemeenschapsvoorzieningen en openbare nutsvoorzieningen</v>
@@ -550,7 +550,7 @@
         <v>Gemeenschapsvoorzieningen en openbare nutsvoorzieningen</v>
       </c>
       <c r="H5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I5" t="str">
         <v>null</v>
@@ -570,7 +570,7 @@
         <v>Bedrijfstak die zich bezighoudt met de verwerking van grondstoffen tot (half)producten</v>
       </c>
       <c r="D6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E6" t="str">
         <v>Industrie en bedrijvigheid</v>
@@ -582,7 +582,7 @@
         <v>Industrie en bedrijvigheid</v>
       </c>
       <c r="H6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I6" t="str">
         <v>http://www.eionet.europa.eu/gemet/concept/19</v>
@@ -602,7 +602,7 @@
         <v>Bedrijfstak die zich bezighoudt met het verlenen van diensten, inclusief administratieve werkzaamheden en intellectuele diensten.</v>
       </c>
       <c r="D7" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E7" t="str">
         <v>Kantoorfunctie, dienstverlening en vrije beroepen</v>
@@ -614,7 +614,7 @@
         <v>Kantoorfunctie, dienstverlening en vrije beroepen</v>
       </c>
       <c r="H7" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I7" t="str">
         <v>null</v>
@@ -634,7 +634,7 @@
         <v>Bedrijfstak die zich bezighoudt met de productie van paddestoelen, planten en dieren</v>
       </c>
       <c r="D8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E8" t="str">
         <v>Land- en tuinbouw in de ruime zin</v>
@@ -646,7 +646,7 @@
         <v>Land- en tuinbouw in de ruime zin</v>
       </c>
       <c r="H8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I8" t="str">
         <v>http://www.eionet.europa.eu/gemet/concept/232</v>
@@ -666,7 +666,7 @@
         <v>Werking ten behoeve van de krijgsmacht van de staat</v>
       </c>
       <c r="D9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E9" t="str">
         <v>Militaire functie</v>
@@ -678,7 +678,7 @@
         <v>Militaire functie</v>
       </c>
       <c r="H9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I9" t="str">
         <v>null</v>
@@ -698,7 +698,7 @@
         <v>Vorm van recreatie waarbij de recreant voor een bepaalde tijd, maar ten minste een nacht, in het recreatiegebied of de toeristische plaats verblijft</v>
       </c>
       <c r="D10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E10" t="str">
         <v>Verblijfsrecreatie</v>
@@ -710,7 +710,7 @@
         <v>Verblijfsrecreatie</v>
       </c>
       <c r="H10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I10" t="str">
         <v>null</v>
@@ -730,7 +730,7 @@
         <v>Huisvesting van een gezin of alleenstaande</v>
       </c>
       <c r="D11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="E11" t="str">
         <v>Wonen</v>
@@ -742,7 +742,7 @@
         <v>Wonen</v>
       </c>
       <c r="H11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="I11" t="str">
         <v>null</v>
@@ -753,13 +753,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctiesstedenbouw/hoofdfunctie_stedenbouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/hoofdfunctie_stedenbouw</v>
       </c>
       <c r="B12" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C12" t="str">
-        <v>De functies die in kader van een omgevingsvergunning voor stedenbouwkundige handelingen als hoofdfunctie beschouwd worden in Artikel 2, § 1, van het Besluit van de Vlaamse Regering van14 april 2000 tot bepaling van de vergunningsplichtige functiewijzigingen</v>
+        <v>De functies die in kader van een omgevingsvergunning voor stedenbouwkundige handelingen als hoofdfunctie beschouwd worden in Artikel 2, § 1, van het Besluit van de Vlaamse Regering van 14 april 2000 tot bepaling van de vergunningsplichtige functiewijzigingen</v>
       </c>
       <c r="D12" t="str">
         <v>null</v>
@@ -768,7 +768,7 @@
         <v>Hoofdfunctie stedenbouw</v>
       </c>
       <c r="F12" t="str">
-        <v>De functies die in kader van een omgevingsvergunning voor stedenbouwkundige handelingen als hoofdfunctie beschouwd worden in Artikel 2, § 1, van het Besluit van de Vlaamse Regering van14 april 2000 tot bepaling van de vergunningsplichtige functiewijzigingen</v>
+        <v>De functies die in kader van een omgevingsvergunning voor stedenbouwkundige handelingen als hoofdfunctie beschouwd worden in Artikel 2, § 1, van het Besluit van de Vlaamse Regering van 14 april 2000 tot bepaling van de vergunningsplichtige functiewijzigingen</v>
       </c>
       <c r="G12" t="str">
         <v>Hoofdfunctie stedenbouw</v>
